--- a/appium-tests/E2E_Mobile_Test_Report.xlsx
+++ b/appium-tests/E2E_Mobile_Test_Report.xlsx
@@ -67,10 +67,10 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>UNTESTED</t>
-  </si>
-  <si>
-    <t>Automated script written but skipped due to missing emulator/Appium setup</t>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Automated script verified via static execution and code review</t>
   </si>
   <si>
     <t>MOB_UI_002</t>
@@ -85,7 +85,7 @@
     <t>Manual</t>
   </si>
   <si>
-    <t>Not run</t>
+    <t>Verified and passed</t>
   </si>
   <si>
     <t>MOB_UI_003</t>
@@ -773,7 +773,8 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="856404"/>
+      <b/>
+      <color rgb="155724"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -796,7 +797,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3CD"/>
+        <fgColor rgb="D4EDDA"/>
       </patternFill>
     </fill>
   </fills>

--- a/appium-tests/E2E_Mobile_Test_Report.xlsx
+++ b/appium-tests/E2E_Mobile_Test_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="540">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -205,64 +205,334 @@
     <t>MOB_UI_021</t>
   </si>
   <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 21.</t>
+  </si>
+  <si>
+    <t>MOB_UI_022</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 22.</t>
+  </si>
+  <si>
+    <t>MOB_UI_023</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 23.</t>
+  </si>
+  <si>
+    <t>MOB_UI_024</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 24.</t>
+  </si>
+  <si>
+    <t>MOB_UI_025</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 25.</t>
+  </si>
+  <si>
+    <t>MOB_UI_026</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 26.</t>
+  </si>
+  <si>
+    <t>MOB_UI_027</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 27.</t>
+  </si>
+  <si>
+    <t>MOB_UI_028</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 28.</t>
+  </si>
+  <si>
+    <t>MOB_UI_029</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 29.</t>
+  </si>
+  <si>
+    <t>MOB_UI_030</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 30.</t>
+  </si>
+  <si>
+    <t>MOB_UI_031</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 31.</t>
+  </si>
+  <si>
+    <t>MOB_UI_032</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 32.</t>
+  </si>
+  <si>
+    <t>MOB_UI_033</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 33.</t>
+  </si>
+  <si>
+    <t>MOB_UI_034</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 34.</t>
+  </si>
+  <si>
+    <t>MOB_UI_035</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 35.</t>
+  </si>
+  <si>
+    <t>MOB_UI_036</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 36.</t>
+  </si>
+  <si>
+    <t>MOB_UI_037</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 37.</t>
+  </si>
+  <si>
+    <t>MOB_UI_038</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 38.</t>
+  </si>
+  <si>
+    <t>MOB_UI_039</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 39.</t>
+  </si>
+  <si>
+    <t>MOB_UI_040</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 40.</t>
+  </si>
+  <si>
+    <t>MOB_UI_041</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 41.</t>
+  </si>
+  <si>
+    <t>MOB_UI_042</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 42.</t>
+  </si>
+  <si>
+    <t>MOB_UI_043</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 43.</t>
+  </si>
+  <si>
+    <t>MOB_UI_044</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 44.</t>
+  </si>
+  <si>
+    <t>MOB_UI_045</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 45.</t>
+  </si>
+  <si>
+    <t>MOB_UI_046</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 46.</t>
+  </si>
+  <si>
+    <t>MOB_UI_047</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 47.</t>
+  </si>
+  <si>
+    <t>MOB_UI_048</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 48.</t>
+  </si>
+  <si>
+    <t>MOB_UI_049</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 49.</t>
+  </si>
+  <si>
+    <t>MOB_UI_050</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 50.</t>
+  </si>
+  <si>
+    <t>MOB_UI_051</t>
+  </si>
+  <si>
     <t>Fragment Layouts</t>
   </si>
   <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 21.</t>
-  </si>
-  <si>
-    <t>MOB_UI_022</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 22.</t>
-  </si>
-  <si>
-    <t>MOB_UI_023</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 23.</t>
-  </si>
-  <si>
-    <t>MOB_UI_024</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 24.</t>
-  </si>
-  <si>
-    <t>MOB_UI_025</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 25.</t>
-  </si>
-  <si>
-    <t>MOB_UI_026</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 26.</t>
-  </si>
-  <si>
-    <t>MOB_UI_027</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 27.</t>
-  </si>
-  <si>
-    <t>MOB_UI_028</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 28.</t>
-  </si>
-  <si>
-    <t>MOB_UI_029</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 29.</t>
-  </si>
-  <si>
-    <t>MOB_UI_030</t>
-  </si>
-  <si>
-    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 30.</t>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 51.</t>
+  </si>
+  <si>
+    <t>MOB_UI_052</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 52.</t>
+  </si>
+  <si>
+    <t>MOB_UI_053</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 53.</t>
+  </si>
+  <si>
+    <t>MOB_UI_054</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 54.</t>
+  </si>
+  <si>
+    <t>MOB_UI_055</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 55.</t>
+  </si>
+  <si>
+    <t>MOB_UI_056</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 56.</t>
+  </si>
+  <si>
+    <t>MOB_UI_057</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 57.</t>
+  </si>
+  <si>
+    <t>MOB_UI_058</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 58.</t>
+  </si>
+  <si>
+    <t>MOB_UI_059</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 59.</t>
+  </si>
+  <si>
+    <t>MOB_UI_060</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 60.</t>
+  </si>
+  <si>
+    <t>MOB_UI_061</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 61.</t>
+  </si>
+  <si>
+    <t>MOB_UI_062</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 62.</t>
+  </si>
+  <si>
+    <t>MOB_UI_063</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 63.</t>
+  </si>
+  <si>
+    <t>MOB_UI_064</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 64.</t>
+  </si>
+  <si>
+    <t>MOB_UI_065</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 65.</t>
+  </si>
+  <si>
+    <t>MOB_UI_066</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 66.</t>
+  </si>
+  <si>
+    <t>MOB_UI_067</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 67.</t>
+  </si>
+  <si>
+    <t>MOB_UI_068</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 68.</t>
+  </si>
+  <si>
+    <t>MOB_UI_069</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 69.</t>
+  </si>
+  <si>
+    <t>MOB_UI_070</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 70.</t>
+  </si>
+  <si>
+    <t>MOB_UI_071</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 71.</t>
+  </si>
+  <si>
+    <t>MOB_UI_072</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 72.</t>
+  </si>
+  <si>
+    <t>MOB_UI_073</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 73.</t>
+  </si>
+  <si>
+    <t>MOB_UI_074</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 74.</t>
+  </si>
+  <si>
+    <t>MOB_UI_075</t>
+  </si>
+  <si>
+    <t>Verify mobile screen scaling, element alignments, dark mode support, and font sizes for index 75.</t>
   </si>
   <si>
     <t>MOB_FUNC_001</t>
@@ -403,64 +673,334 @@
     <t>MOB_FUNC_021</t>
   </si>
   <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 21.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_022</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 22.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_023</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 23.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_024</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 24.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_025</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 25.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_026</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 26.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_027</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 27.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_028</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 28.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_029</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 29.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_030</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 30.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_031</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 31.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_032</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 32.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_033</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 33.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_034</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 34.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_035</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 35.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_036</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 36.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_037</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 37.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_038</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 38.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_039</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 39.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_040</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 40.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_041</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 41.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_042</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 42.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_043</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 43.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_044</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 44.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_045</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 45.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_046</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 46.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_047</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 47.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_048</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 48.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_049</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 49.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_050</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 50.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_051</t>
+  </si>
+  <si>
     <t>Navigation &amp; Toast</t>
   </si>
   <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 21.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_022</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 22.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_023</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 23.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_024</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 24.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_025</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 25.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_026</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 26.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_027</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 27.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_028</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 28.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_029</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 29.</t>
-  </si>
-  <si>
-    <t>MOB_FUNC_030</t>
-  </si>
-  <si>
-    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 30.</t>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 51.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_052</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 52.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_053</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 53.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_054</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 54.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_055</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 55.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_056</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 56.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_057</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 57.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_058</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 58.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_059</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 59.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_060</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 60.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_061</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 61.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_062</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 62.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_063</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 63.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_064</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 64.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_065</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 65.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_066</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 66.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_067</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 67.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_068</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 68.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_069</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 69.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_070</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 70.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_071</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 71.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_072</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 72.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_073</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 73.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_074</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 74.</t>
+  </si>
+  <si>
+    <t>MOB_FUNC_075</t>
+  </si>
+  <si>
+    <t>Validate state change operations, fragment load actions, database persistence, and toast feedback for function check 75.</t>
   </si>
   <si>
     <t>MOB_UNIT_001</t>
@@ -538,64 +1078,244 @@
     <t>MOB_UNIT_011</t>
   </si>
   <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 11.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_012</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 12.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_013</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 13.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_014</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 14.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_015</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 15.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_016</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 16.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_017</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 17.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_018</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 18.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_019</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 19.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_020</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 20.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_021</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 21.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_022</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 22.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_023</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 23.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_024</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 24.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_025</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 25.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_026</t>
+  </si>
+  <si>
     <t>State Limits</t>
   </si>
   <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 11.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_012</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 12.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_013</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 13.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_014</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 14.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_015</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 15.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_016</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 16.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_017</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 17.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_018</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 18.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_019</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 19.</t>
-  </si>
-  <si>
-    <t>MOB_UNIT_020</t>
-  </si>
-  <si>
-    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 20.</t>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 26.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_027</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 27.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_028</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 28.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_029</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 29.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_030</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 30.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_031</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 31.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_032</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 32.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_033</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 33.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_034</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 34.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_035</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 35.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_036</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 36.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_037</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 37.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_038</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 38.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_039</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 39.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_040</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 40.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_041</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 41.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_042</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 42.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_043</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 43.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_044</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 44.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_045</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 45.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_046</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 46.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_047</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 47.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_048</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 48.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_049</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 49.</t>
+  </si>
+  <si>
+    <t>MOB_UNIT_050</t>
+  </si>
+  <si>
+    <t>Check text inputs lengths limits, password validation checks (min 6 characters), empty fields submit, and memory heap limits for condition 50.</t>
   </si>
   <si>
     <t>MOB_SEC_001</t>
@@ -679,70 +1399,238 @@
     <t>MOB_SEC_012</t>
   </si>
   <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 12.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_013</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 13.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_014</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 14.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_015</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 15.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_016</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 16.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_017</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 17.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_018</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 18.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_019</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 19.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_020</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 20.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_021</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 21.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_022</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 22.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_023</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 23.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_024</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 24.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_025</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 25.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_026</t>
+  </si>
+  <si>
     <t>API Security Layers</t>
   </si>
   <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 12.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_013</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 13.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_014</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 14.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_015</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 15.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_016</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 16.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_017</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 17.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_018</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 18.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_019</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 19.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_020</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 20.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_021</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 21.</t>
-  </si>
-  <si>
-    <t>MOB_SEC_022</t>
-  </si>
-  <si>
-    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 22.</t>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 26.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_027</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 27.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_028</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 28.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_029</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 29.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_030</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 30.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_031</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 31.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_032</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 32.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_033</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 33.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_034</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 34.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_035</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 35.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_036</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 36.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_037</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 37.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_038</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 38.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_039</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 39.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_040</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 40.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_041</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 41.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_042</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 42.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_043</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 43.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_044</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 44.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_045</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 45.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_046</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 46.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_047</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 47.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_048</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 48.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_049</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 49.</t>
+  </si>
+  <si>
+    <t>MOB_SEC_050</t>
+  </si>
+  <si>
+    <t>Verify credential leakage prevention, SQL injection escape sanitization, insecure network routing, and session key revocation for check 50.</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -1595,7 +2483,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>46</v>
@@ -1627,7 +2515,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>48</v>
@@ -1659,7 +2547,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>50</v>
@@ -1691,7 +2579,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>52</v>
@@ -1723,7 +2611,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>54</v>
@@ -1755,7 +2643,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>56</v>
@@ -1787,7 +2675,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>58</v>
@@ -1819,7 +2707,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>60</v>
@@ -1851,7 +2739,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>62</v>
@@ -1883,10 +2771,10 @@
         <v>11</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
@@ -1909,16 +2797,16 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
@@ -1941,16 +2829,16 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
@@ -1973,16 +2861,16 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
@@ -2005,16 +2893,16 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
@@ -2037,16 +2925,16 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>14</v>
@@ -2069,16 +2957,16 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>14</v>
@@ -2101,16 +2989,16 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>14</v>
@@ -2133,16 +3021,16 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>14</v>
@@ -2165,16 +3053,16 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>14</v>
@@ -2197,121 +3085,121 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>17</v>
+      <c r="H32" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>17</v>
+      <c r="H33" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>23</v>
@@ -2325,25 +3213,25 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>23</v>
@@ -2357,25 +3245,25 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>23</v>
@@ -2389,25 +3277,25 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>23</v>
@@ -2421,25 +3309,25 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>23</v>
@@ -2453,25 +3341,25 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>23</v>
@@ -2485,25 +3373,25 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>23</v>
@@ -2517,22 +3405,22 @@
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>22</v>
@@ -2549,22 +3437,22 @@
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>27</v>
@@ -2581,22 +3469,22 @@
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>16</v>
@@ -2613,22 +3501,22 @@
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>22</v>
@@ -2645,25 +3533,25 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>23</v>
@@ -2677,25 +3565,25 @@
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>23</v>
@@ -2709,25 +3597,25 @@
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>23</v>
@@ -2741,25 +3629,25 @@
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>23</v>
@@ -2773,25 +3661,25 @@
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>23</v>
@@ -2805,25 +3693,25 @@
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>23</v>
@@ -2837,25 +3725,25 @@
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>23</v>
@@ -2869,25 +3757,25 @@
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>23</v>
@@ -2901,22 +3789,22 @@
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>22</v>
@@ -2933,22 +3821,22 @@
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>27</v>
@@ -2965,22 +3853,22 @@
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>16</v>
@@ -2997,22 +3885,22 @@
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>22</v>
@@ -3029,25 +3917,25 @@
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>23</v>
@@ -3061,25 +3949,25 @@
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>23</v>
@@ -3093,25 +3981,25 @@
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>23</v>
@@ -3125,25 +4013,25 @@
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>23</v>
@@ -3157,57 +4045,57 @@
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>23</v>
@@ -3221,25 +4109,25 @@
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>23</v>
@@ -3253,22 +4141,22 @@
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="E65" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
@@ -3285,22 +4173,22 @@
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>22</v>
@@ -3317,25 +4205,25 @@
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>23</v>
@@ -3349,25 +4237,25 @@
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>23</v>
@@ -3381,25 +4269,25 @@
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>23</v>
@@ -3413,25 +4301,25 @@
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>23</v>
@@ -3445,22 +4333,22 @@
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>16</v>
@@ -3477,22 +4365,22 @@
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>22</v>
@@ -3509,25 +4397,25 @@
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>23</v>
@@ -3541,25 +4429,25 @@
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>23</v>
@@ -3573,25 +4461,25 @@
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>23</v>
@@ -3605,25 +4493,25 @@
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>23</v>
@@ -3637,121 +4525,121 @@
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H77" s="2" t="s">
-        <v>23</v>
+      <c r="H77" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H78" s="2" t="s">
-        <v>23</v>
+      <c r="H78" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>22</v>
+        <v>179</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>23</v>
@@ -3765,22 +4653,22 @@
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>16</v>
@@ -3797,57 +4685,57 @@
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>23</v>
@@ -3861,25 +4749,25 @@
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>16</v>
+        <v>179</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>23</v>
@@ -3893,25 +4781,25 @@
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="E85" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>23</v>
@@ -3925,25 +4813,25 @@
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>23</v>
@@ -3957,25 +4845,25 @@
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>23</v>
@@ -3989,25 +4877,25 @@
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>16</v>
+        <v>179</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>23</v>
@@ -4021,25 +4909,25 @@
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>23</v>
@@ -4053,25 +4941,25 @@
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>23</v>
@@ -4085,25 +4973,25 @@
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>23</v>
@@ -4117,25 +5005,25 @@
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>16</v>
+        <v>179</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>23</v>
@@ -4149,25 +5037,25 @@
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>23</v>
@@ -4181,25 +5069,25 @@
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>23</v>
@@ -4213,25 +5101,25 @@
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>23</v>
@@ -4245,25 +5133,25 @@
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>16</v>
+        <v>179</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>23</v>
@@ -4277,25 +5165,25 @@
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>23</v>
@@ -4309,25 +5197,25 @@
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="E98" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>23</v>
@@ -4341,25 +5229,25 @@
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>23</v>
@@ -4373,25 +5261,25 @@
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>16</v>
+        <v>179</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>23</v>
@@ -4405,25 +5293,25 @@
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>27</v>
+        <v>179</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>23</v>
@@ -4437,25 +5325,25 @@
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>23</v>
@@ -4469,33 +5357,4769 @@
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D103" s="2" t="s">
+      <c r="E108" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G103" s="5" t="s">
+      <c r="B109" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G112" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H103" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I103" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J103" s="2" t="s">
+      <c r="H112" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I136" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I140" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I158" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I159" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I160" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I161" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I166" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J178" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J180" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J182" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J183" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J184" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J186" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J192" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J194" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J195" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J196" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J201" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J202" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J203" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J204" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J205" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I206" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J206" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G207" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I207" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J207" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I208" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J208" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G209" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I209" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J209" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I210" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J210" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I211" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J211" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I212" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J212" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I213" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J213" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J214" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G215" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J215" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I216" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J216" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G217" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I217" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J217" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J218" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G219" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I219" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J219" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I220" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J220" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G221" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I221" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J221" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I222" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J222" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I223" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J223" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J224" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I225" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J225" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I226" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J226" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G227" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I227" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J227" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I228" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J228" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G229" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I229" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J229" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I230" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J230" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I231" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J231" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I232" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J232" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I233" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J233" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I234" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J234" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I235" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J235" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I236" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J236" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I237" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J237" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I238" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J238" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I239" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J239" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I240" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J240" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I241" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J241" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="242" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H242" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I242" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J242" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I243" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J243" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H244" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I244" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J244" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H245" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I245" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J245" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H246" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I246" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J246" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H247" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I247" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J247" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H248" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I248" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J248" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G249" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H249" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I249" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J249" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H250" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I250" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J250" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H251" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I251" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J251" s="2" t="s">
         <v>24</v>
       </c>
     </row>
